--- a/sources/3C_Manha_1_Bimestre.xlsx
+++ b/sources/3C_Manha_1_Bimestre.xlsx
@@ -257,6 +257,12 @@
     <x:t>85%</x:t>
   </x:si>
   <x:si>
+    <x:t>DANIEL SOUZA GONZAGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
     <x:t>DAVID FERRAZ FROTA AFONSO</x:t>
   </x:si>
   <x:si>
@@ -299,6 +305,9 @@
     <x:t>68%</x:t>
   </x:si>
   <x:si>
+    <x:t>HERLAN SATURNINO BAZAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>IGOR FERREIRA BASTOS</x:t>
   </x:si>
   <x:si>
@@ -380,9 +389,6 @@
     <x:t>MATHEUS CARDOSO DE OLIVEIRA</x:t>
   </x:si>
   <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
     <x:t>MATHEUS PEREIRA SALES</x:t>
   </x:si>
   <x:si>
@@ -432,12 +438,6 @@
   </x:si>
   <x:si>
     <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DANIEL SOUZA GONZAGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERLAN SATURNINO BAZAN</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -2311,7 +2311,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
         <x:v>46</x:v>
@@ -2323,7 +2323,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
         <x:v>46</x:v>
@@ -2335,10 +2335,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>46</x:v>
@@ -2347,13 +2347,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S20" s="12">
         <x:v>8</x:v>
@@ -2371,10 +2371,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>46</x:v>
@@ -2383,7 +2383,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
         <x:v>46</x:v>
@@ -2407,10 +2407,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
         <x:v>46</x:v>
@@ -2428,21 +2428,21 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ20" s="12">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AS20" s="12">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:46">
       <x:c r="A21" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>43</x:v>
@@ -2463,10 +2463,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
         <x:v>46</x:v>
@@ -2475,10 +2475,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>46</x:v>
@@ -2487,13 +2487,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S21" s="12">
         <x:v>9</x:v>
@@ -2511,10 +2511,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>46</x:v>
@@ -2523,10 +2523,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>46</x:v>
@@ -2538,7 +2538,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>46</x:v>
@@ -2547,10 +2547,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>46</x:v>
@@ -2562,22 +2562,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ21" s="12">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS21" s="12">
-        <x:v>26</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:46">
@@ -2591,10 +2591,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
         <x:v>46</x:v>
@@ -2603,10 +2603,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
         <x:v>46</x:v>
@@ -2615,10 +2615,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N22" s="12" t="s">
         <x:v>46</x:v>
@@ -2627,13 +2627,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="P22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S22" s="12">
         <x:v>10</x:v>
@@ -2651,10 +2651,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="X22" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Y22" s="12" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="Y22" s="12" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
         <x:v>46</x:v>
@@ -2663,10 +2663,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>46</x:v>
@@ -2678,7 +2678,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
         <x:v>46</x:v>
@@ -2687,7 +2687,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
         <x:v>50</x:v>
@@ -2702,27 +2702,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ22" s="12">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="AS22" s="12">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:46">
       <x:c r="A23" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>43</x:v>
@@ -2734,7 +2734,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
         <x:v>46</x:v>
@@ -2743,10 +2743,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
         <x:v>46</x:v>
@@ -2755,10 +2755,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>46</x:v>
@@ -2767,13 +2767,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S23" s="12">
         <x:v>11</x:v>
@@ -2791,10 +2791,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
         <x:v>46</x:v>
@@ -2803,10 +2803,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
         <x:v>46</x:v>
@@ -2818,7 +2818,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
         <x:v>46</x:v>
@@ -2830,7 +2830,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
         <x:v>46</x:v>
@@ -2842,19 +2842,19 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ23" s="12">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AS23" s="12">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
         <x:v>84</x:v>
@@ -2871,10 +2871,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>46</x:v>
@@ -2883,10 +2883,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>46</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
         <x:v>49</x:v>
@@ -2907,13 +2907,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S24" s="12">
         <x:v>12</x:v>
@@ -2946,7 +2946,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>46</x:v>
@@ -2967,10 +2967,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>46</x:v>
@@ -2982,27 +2982,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ24" s="12">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AS24" s="12">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:46">
       <x:c r="A25" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>43</x:v>
@@ -3011,10 +3011,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
         <x:v>46</x:v>
@@ -3023,10 +3023,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
         <x:v>46</x:v>
@@ -3035,10 +3035,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N25" s="12" t="s">
         <x:v>46</x:v>
@@ -3047,13 +3047,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="P25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S25" s="12">
         <x:v>13</x:v>
@@ -3074,7 +3074,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
         <x:v>46</x:v>
@@ -3083,10 +3083,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="s">
         <x:v>46</x:v>
@@ -3098,7 +3098,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH25" s="12" t="s">
         <x:v>46</x:v>
@@ -3107,10 +3107,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>46</x:v>
@@ -3122,39 +3122,39 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ25" s="12">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AS25" s="12">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:46">
       <x:c r="A26" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
         <x:v>46</x:v>
@@ -3163,22 +3163,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
         <x:v>46</x:v>
@@ -3187,10 +3187,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R26" s="12" t="s">
         <x:v>46</x:v>
@@ -3211,10 +3211,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
         <x:v>46</x:v>
@@ -3223,10 +3223,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="s">
         <x:v>46</x:v>
@@ -3235,10 +3235,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>46</x:v>
@@ -3247,7 +3247,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
         <x:v>46</x:v>
@@ -3259,42 +3259,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AN26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ26" s="12">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AS26" s="12">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:46">
       <x:c r="A27" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
         <x:v>46</x:v>
@@ -3303,22 +3303,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>46</x:v>
@@ -3327,13 +3327,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S27" s="12">
         <x:v>15</x:v>
@@ -3351,10 +3351,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
         <x:v>46</x:v>
@@ -3363,10 +3363,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>46</x:v>
@@ -3375,10 +3375,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>46</x:v>
@@ -3387,10 +3387,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>46</x:v>
@@ -3399,25 +3399,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AS27" s="12">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="AT27" s="12" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="AS27" s="12">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="AT27" s="12" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:46">
@@ -3425,16 +3425,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
         <x:v>46</x:v>
@@ -3443,22 +3443,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>46</x:v>
@@ -3470,7 +3470,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
         <x:v>46</x:v>
@@ -3491,10 +3491,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
         <x:v>46</x:v>
@@ -3503,10 +3503,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>46</x:v>
@@ -3515,10 +3515,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>46</x:v>
@@ -3527,7 +3527,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
         <x:v>46</x:v>
@@ -3539,25 +3539,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ28" s="12">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AS28" s="12">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:46">
@@ -3574,7 +3574,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>46</x:v>
@@ -3583,10 +3583,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
         <x:v>46</x:v>
@@ -3595,10 +3595,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
         <x:v>46</x:v>
@@ -3607,13 +3607,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S29" s="12">
         <x:v>17</x:v>
@@ -3634,7 +3634,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
         <x:v>46</x:v>
@@ -3646,7 +3646,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>46</x:v>
@@ -3658,7 +3658,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>46</x:v>
@@ -3667,7 +3667,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
         <x:v>49</x:v>
@@ -3682,36 +3682,36 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ29" s="12">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AS29" s="12">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:46">
       <x:c r="A30" s="11" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
         <x:v>45</x:v>
@@ -3723,22 +3723,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>46</x:v>
@@ -3747,13 +3747,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S30" s="12">
         <x:v>18</x:v>
@@ -3771,10 +3771,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
         <x:v>46</x:v>
@@ -3783,10 +3783,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>46</x:v>
@@ -3795,10 +3795,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>46</x:v>
@@ -3807,10 +3807,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>46</x:v>
@@ -3819,30 +3819,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ30" s="12">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AS30" s="12">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:46">
       <x:c r="A31" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>43</x:v>
@@ -3851,10 +3851,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>46</x:v>
@@ -3866,7 +3866,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
         <x:v>46</x:v>
@@ -3887,13 +3887,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
@@ -3914,7 +3914,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
         <x:v>46</x:v>
@@ -3926,7 +3926,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
         <x:v>46</x:v>
@@ -3938,7 +3938,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
         <x:v>46</x:v>
@@ -3950,7 +3950,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>46</x:v>
@@ -3962,27 +3962,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AS31" s="12">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:46">
       <x:c r="A32" s="11" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>43</x:v>
@@ -3991,10 +3991,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>46</x:v>
@@ -4003,10 +4003,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
         <x:v>46</x:v>
@@ -4015,10 +4015,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>46</x:v>
@@ -4027,13 +4027,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
@@ -4051,10 +4051,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>46</x:v>
@@ -4063,10 +4063,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>46</x:v>
@@ -4078,7 +4078,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>46</x:v>
@@ -4087,10 +4087,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>46</x:v>
@@ -4102,22 +4102,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
-        <x:v>27</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AS32" s="12">
-        <x:v>25</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:46">
@@ -4131,10 +4131,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
         <x:v>46</x:v>
@@ -4146,7 +4146,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
         <x:v>46</x:v>
@@ -4158,7 +4158,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>46</x:v>
@@ -4167,7 +4167,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
         <x:v>49</x:v>
@@ -4191,10 +4191,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>46</x:v>
@@ -4203,10 +4203,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>46</x:v>
@@ -4218,7 +4218,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>46</x:v>
@@ -4230,7 +4230,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>46</x:v>
@@ -4242,27 +4242,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="AS33" s="12">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:46">
       <x:c r="A34" s="11" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>43</x:v>
@@ -4271,10 +4271,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>46</x:v>
@@ -4283,10 +4283,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="I34" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>46</x:v>
@@ -4295,10 +4295,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>46</x:v>
@@ -4307,7 +4307,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
         <x:v>59</x:v>
@@ -4331,10 +4331,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>46</x:v>
@@ -4343,10 +4343,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>46</x:v>
@@ -4358,7 +4358,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>46</x:v>
@@ -4367,10 +4367,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>46</x:v>
@@ -4382,27 +4382,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
-        <x:v>4</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AS34" s="12">
-        <x:v>2</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:46">
       <x:c r="A35" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>43</x:v>
@@ -4411,10 +4411,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>46</x:v>
@@ -4423,10 +4423,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>46</x:v>
@@ -4435,10 +4435,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
         <x:v>46</x:v>
@@ -4447,13 +4447,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S35" s="12">
         <x:v>23</x:v>
@@ -4471,10 +4471,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
         <x:v>46</x:v>
@@ -4483,10 +4483,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>46</x:v>
@@ -4498,7 +4498,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>46</x:v>
@@ -4507,10 +4507,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
         <x:v>46</x:v>
@@ -4522,22 +4522,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ35" s="12">
-        <x:v>6</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AS35" s="12">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:46">
@@ -4545,13 +4545,13 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>46</x:v>
@@ -4563,22 +4563,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
         <x:v>46</x:v>
@@ -4587,13 +4587,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S36" s="12">
         <x:v>24</x:v>
@@ -4611,10 +4611,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
         <x:v>46</x:v>
@@ -4623,10 +4623,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>46</x:v>
@@ -4635,10 +4635,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>46</x:v>
@@ -4647,7 +4647,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
         <x:v>46</x:v>
@@ -4659,25 +4659,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ36" s="12">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS36" s="12">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:46">
@@ -4703,10 +4703,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>46</x:v>
@@ -4715,7 +4715,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
         <x:v>46</x:v>
@@ -4727,13 +4727,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S37" s="12">
         <x:v>25</x:v>
@@ -4751,10 +4751,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
         <x:v>46</x:v>
@@ -4763,7 +4763,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
         <x:v>45</x:v>
@@ -4787,10 +4787,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>46</x:v>
@@ -4802,7 +4802,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
         <x:v>46</x:v>
@@ -4814,10 +4814,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="AS37" s="12">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:46">
@@ -4825,13 +4825,13 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>46</x:v>
@@ -4843,22 +4843,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>46</x:v>
@@ -4867,10 +4867,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
         <x:v>46</x:v>
@@ -4891,7 +4891,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
         <x:v>59</x:v>
@@ -4903,10 +4903,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
         <x:v>46</x:v>
@@ -4915,10 +4915,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>46</x:v>
@@ -4927,7 +4927,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
         <x:v>46</x:v>
@@ -4939,30 +4939,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ38" s="12">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AS38" s="12">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:46">
       <x:c r="A39" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>43</x:v>
@@ -4971,10 +4971,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>46</x:v>
@@ -4983,10 +4983,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>46</x:v>
@@ -4995,10 +4995,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>46</x:v>
@@ -5007,13 +5007,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S39" s="12">
         <x:v>27</x:v>
@@ -5031,10 +5031,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>46</x:v>
@@ -5043,10 +5043,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>46</x:v>
@@ -5058,7 +5058,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>46</x:v>
@@ -5067,10 +5067,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>46</x:v>
@@ -5082,27 +5082,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ39" s="12">
-        <x:v>98</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS39" s="12">
-        <x:v>87</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:46">
       <x:c r="A40" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>43</x:v>
@@ -5111,7 +5111,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>46</x:v>
@@ -5123,7 +5123,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
         <x:v>59</x:v>
@@ -5135,7 +5135,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
         <x:v>46</x:v>
@@ -5150,10 +5150,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
@@ -5174,7 +5174,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>46</x:v>
@@ -5186,7 +5186,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>46</x:v>
@@ -5207,10 +5207,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>46</x:v>
@@ -5222,27 +5222,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS40" s="12">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:46">
       <x:c r="A41" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>43</x:v>
@@ -5251,10 +5251,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>46</x:v>
@@ -5263,10 +5263,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>46</x:v>
@@ -5275,10 +5275,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>46</x:v>
@@ -5287,13 +5287,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
@@ -5311,10 +5311,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="Y41" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="Y41" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>46</x:v>
@@ -5323,10 +5323,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>46</x:v>
@@ -5338,7 +5338,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>46</x:v>
@@ -5347,10 +5347,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>46</x:v>
@@ -5362,27 +5362,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
-        <x:v>0</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="AS41" s="12">
-        <x:v>0</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:46">
       <x:c r="A42" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
         <x:v>43</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>46</x:v>
@@ -5427,13 +5427,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Q42" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q42" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="R42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S42" s="12">
         <x:v>30</x:v>
@@ -5451,10 +5451,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>46</x:v>
@@ -5463,10 +5463,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>46</x:v>
@@ -5487,10 +5487,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>46</x:v>
@@ -5502,22 +5502,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AS42" s="12">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:46">
@@ -5531,7 +5531,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
         <x:v>46</x:v>
@@ -5543,7 +5543,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
         <x:v>46</x:v>
@@ -5555,7 +5555,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
         <x:v>46</x:v>
@@ -5567,7 +5567,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
         <x:v>46</x:v>
@@ -5591,7 +5591,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
         <x:v>46</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
         <x:v>46</x:v>
@@ -5642,22 +5642,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AS43" s="12">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:46">
@@ -5671,7 +5671,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
         <x:v>46</x:v>
@@ -5683,10 +5683,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
         <x:v>46</x:v>
@@ -5695,7 +5695,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
         <x:v>46</x:v>
@@ -5707,7 +5707,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
         <x:v>46</x:v>
@@ -5731,7 +5731,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
         <x:v>46</x:v>
@@ -5743,7 +5743,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
         <x:v>46</x:v>
@@ -5767,7 +5767,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
         <x:v>46</x:v>
@@ -5788,16 +5788,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AS44" s="12">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:46">
@@ -5811,7 +5811,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>46</x:v>
@@ -5838,7 +5838,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>46</x:v>
@@ -5847,13 +5847,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
@@ -5871,10 +5871,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>46</x:v>
@@ -5886,7 +5886,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>46</x:v>
@@ -5907,10 +5907,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>46</x:v>
@@ -5928,16 +5928,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AS45" s="12">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:46">
@@ -5951,10 +5951,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>46</x:v>
@@ -5963,10 +5963,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>46</x:v>
@@ -5975,10 +5975,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>46</x:v>
@@ -5987,13 +5987,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S46" s="12">
         <x:v>34</x:v>
@@ -6011,10 +6011,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
         <x:v>46</x:v>
@@ -6023,10 +6023,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>46</x:v>
@@ -6038,7 +6038,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>46</x:v>
@@ -6047,10 +6047,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>46</x:v>
@@ -6062,27 +6062,27 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
-        <x:v>46</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="AS46" s="12">
-        <x:v>44</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:46">
       <x:c r="A47" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>43</x:v>
@@ -6094,7 +6094,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>46</x:v>
@@ -6103,10 +6103,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>46</x:v>
@@ -6115,10 +6115,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>46</x:v>
@@ -6127,13 +6127,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S47" s="12">
         <x:v>35</x:v>
@@ -6154,7 +6154,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>46</x:v>
@@ -6166,7 +6166,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>46</x:v>
@@ -6178,7 +6178,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>46</x:v>
@@ -6187,10 +6187,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>46</x:v>
@@ -6202,36 +6202,36 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
-        <x:v>70</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AS47" s="12">
-        <x:v>63</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:46">
       <x:c r="A48" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
         <x:v>59</x:v>
@@ -6243,22 +6243,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>46</x:v>
@@ -6267,13 +6267,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
@@ -6291,10 +6291,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>46</x:v>
@@ -6303,10 +6303,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>46</x:v>
@@ -6315,10 +6315,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>46</x:v>
@@ -6327,10 +6327,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>46</x:v>
@@ -6339,30 +6339,30 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="AS48" s="12">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:46">
       <x:c r="A49" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>43</x:v>
@@ -6371,10 +6371,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>46</x:v>
@@ -6383,10 +6383,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>46</x:v>
@@ -6395,10 +6395,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>46</x:v>
@@ -6407,13 +6407,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S49" s="12">
         <x:v>37</x:v>
@@ -6434,7 +6434,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>46</x:v>
@@ -6446,7 +6446,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>46</x:v>
@@ -6458,7 +6458,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>46</x:v>
@@ -6467,10 +6467,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>46</x:v>
@@ -6482,30 +6482,30 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AS49" s="12">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:46">
       <x:c r="A50" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
@@ -6514,7 +6514,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>46</x:v>
@@ -6538,7 +6538,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>46</x:v>
@@ -6550,7 +6550,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
         <x:v>46</x:v>
@@ -6574,7 +6574,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>46</x:v>
@@ -6586,7 +6586,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD50" s="12" t="s">
         <x:v>46</x:v>
@@ -6598,7 +6598,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>46</x:v>
@@ -6622,22 +6622,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ50" s="12">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AS50" s="12">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:46">
@@ -6654,7 +6654,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>46</x:v>
@@ -6663,10 +6663,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>46</x:v>
@@ -6675,10 +6675,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>46</x:v>
@@ -6687,13 +6687,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S51" s="12">
         <x:v>39</x:v>
@@ -6714,7 +6714,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>46</x:v>
@@ -6726,7 +6726,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>46</x:v>
@@ -6738,7 +6738,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>46</x:v>
@@ -6747,10 +6747,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>46</x:v>
@@ -6762,22 +6762,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ51" s="12">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AS51" s="12">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:46">
@@ -6785,16 +6785,16 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F52" s="12" t="s">
         <x:v>46</x:v>
@@ -6803,22 +6803,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>46</x:v>
@@ -6827,13 +6827,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R52" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S52" s="12">
         <x:v>40</x:v>
@@ -6851,10 +6851,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
         <x:v>46</x:v>
@@ -6863,10 +6863,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>46</x:v>
@@ -6875,10 +6875,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>46</x:v>
@@ -6887,10 +6887,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>46</x:v>
@@ -6899,30 +6899,30 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ52" s="12">
-        <x:v>76</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AS52" s="12">
-        <x:v>69</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:46">
       <x:c r="A53" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
         <x:v>43</x:v>
@@ -6934,7 +6934,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>46</x:v>
@@ -6943,10 +6943,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>46</x:v>
@@ -6955,7 +6955,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
         <x:v>51</x:v>
@@ -6967,13 +6967,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S53" s="12">
         <x:v>41</x:v>
@@ -6994,7 +6994,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
         <x:v>46</x:v>
@@ -7003,10 +7003,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>46</x:v>
@@ -7018,7 +7018,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>46</x:v>
@@ -7027,10 +7027,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>46</x:v>
@@ -7042,22 +7042,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ53" s="12">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS53" s="12">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:46">
@@ -7065,16 +7065,16 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>46</x:v>
@@ -7083,22 +7083,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>46</x:v>
@@ -7107,13 +7107,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S54" s="12">
         <x:v>42</x:v>
@@ -7131,10 +7131,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
         <x:v>46</x:v>
@@ -7143,10 +7143,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>46</x:v>
@@ -7155,10 +7155,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>46</x:v>
@@ -7167,10 +7167,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>46</x:v>
@@ -7179,30 +7179,30 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
-        <x:v>24</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AS54" s="12">
-        <x:v>24</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:46">
       <x:c r="A55" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>43</x:v>
@@ -7211,10 +7211,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>46</x:v>
@@ -7223,10 +7223,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
         <x:v>46</x:v>
@@ -7235,10 +7235,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>46</x:v>
@@ -7247,13 +7247,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S55" s="12">
         <x:v>43</x:v>
@@ -7271,10 +7271,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z55" s="12" t="s">
         <x:v>46</x:v>
@@ -7283,10 +7283,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>46</x:v>
@@ -7298,7 +7298,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>46</x:v>
@@ -7307,10 +7307,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>46</x:v>
@@ -7322,39 +7322,39 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ55" s="12">
-        <x:v>1</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS55" s="12">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:46">
       <x:c r="A56" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>46</x:v>
@@ -7363,22 +7363,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>46</x:v>
@@ -7390,7 +7390,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>46</x:v>
@@ -7411,10 +7411,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>46</x:v>
@@ -7423,10 +7423,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>46</x:v>
@@ -7435,10 +7435,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>46</x:v>
@@ -7447,7 +7447,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
         <x:v>46</x:v>
@@ -7459,25 +7459,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AQ56" s="12">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="AS56" s="12">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:46">
